--- a/excel/Nordstreet Rima.xlsx
+++ b/excel/Nordstreet Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Nordstreet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F86A774-BA2C-4555-9C0A-36400B9341A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD671DF-CFA4-48F9-95D7-74510A1F52CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="J3" s="8">
         <f ca="1">'Mozūriškių g. 17-3, Vilnius'!B13</f>
-        <v>18</v>
+        <v>-11</v>
       </c>
       <c r="K3" s="8">
         <f ca="1">'Mozūriškių g. 17-3, Vilnius'!S3</f>
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="L3" s="5">
         <f>'Mozūriškių g. 17-3, Vilnius'!N3</f>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>29.990000000000009</v>
+        <v>35.909999999999968</v>
       </c>
       <c r="S3" s="5">
         <f t="shared" ref="S3" si="0">SUM(L3:L27)</f>
@@ -1284,23 +1284,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M27)</f>
-        <v>46.129999999999995</v>
+        <v>52.05</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>698.99</v>
+        <v>704.91</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>78.990000000000009</v>
+        <v>84.909999999999968</v>
       </c>
       <c r="W3" s="16">
         <f>(U3-O3)/O3</f>
-        <v>0.12740322580645164</v>
+        <v>0.13695161290322574</v>
       </c>
       <c r="X3" s="16">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15879907011985778</v>
+        <v>0.15457088351249695</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Mozūriškių g. 17-3, Vilnius'!AA2</f>
@@ -1345,11 +1345,11 @@
       </c>
       <c r="J4" s="8">
         <f ca="1">'Birstyčios g. 27, Vilnius (11)'!B13</f>
-        <v>-53</v>
-      </c>
-      <c r="K4" s="8">
+        <v>-82</v>
+      </c>
+      <c r="K4" s="8" t="str">
         <f ca="1">'Birstyčios g. 27, Vilnius (11)'!S3</f>
-        <v>53</v>
+        <v/>
       </c>
       <c r="L4" s="5">
         <f>'Birstyčios g. 27, Vilnius (11)'!N3</f>
@@ -1357,11 +1357,11 @@
       </c>
       <c r="M4" s="5">
         <f>'Birstyčios g. 27, Vilnius (11)'!P3</f>
-        <v>16.38</v>
+        <v>21.839999999999996</v>
       </c>
       <c r="AC4" s="5" t="str">
         <f ca="1">'Birstyčios g. 27, Vilnius (11)'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="J5" s="8">
         <f ca="1">'Baltų Avenue (2)'!B13</f>
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="K5" s="8" t="str">
         <f ca="1">'Baltų Avenue (2)'!S3</f>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M5" s="5">
         <f>'Baltų Avenue (2)'!P3</f>
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="AC5" s="5" t="str">
         <f ca="1">'Baltų Avenue (2)'!AA2</f>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="J6" s="8">
         <f ca="1">'Liepų g. 3, Vyšniūnai (6)'!B13</f>
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="K6" s="8">
         <f ca="1">'Liepų g. 3, Vyšniūnai (6)'!S3</f>
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="L6" s="5">
         <f>'Liepų g. 3, Vyšniūnai (6)'!N3</f>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="L1" s="16">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.15879907011985778</v>
+        <v>0.15457088351249695</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3379,14 +3379,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="5">
         <f>Apžvalga!U3</f>
-        <v>698.99</v>
+        <v>704.91</v>
       </c>
     </row>
   </sheetData>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D13" s="7">
         <v>46429</v>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="Q3" s="16" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -5137,13 +5137,21 @@
       <c r="F11" s="5">
         <v>0.46</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7">
+        <v>46282</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="0"/>
+        <v>-2</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
@@ -5181,11 +5189,11 @@
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46282</v>
       </c>
       <c r="Z12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
@@ -5194,7 +5202,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="D13" s="7">
         <v>46345</v>
@@ -5923,7 +5931,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
@@ -6106,7 +6114,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -6151,11 +6159,11 @@
       </c>
       <c r="O3" s="5">
         <f>F42</f>
-        <v>17.29</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>16.38</v>
+        <v>21.839999999999996</v>
       </c>
       <c r="Q3" s="16" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -6165,9 +6173,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>53</v>
+        <v/>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -6480,21 +6488,29 @@
         <v>200</v>
       </c>
       <c r="D11" s="7">
-        <v>46213</v>
+        <v>46275</v>
       </c>
       <c r="E11" s="5">
         <v>200</v>
       </c>
       <c r="F11" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>3.2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J11" s="7">
+        <v>46286</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
@@ -6525,11 +6541,11 @@
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46286</v>
       </c>
       <c r="Z12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
@@ -6538,7 +6554,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-53</v>
+        <v>-82</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
@@ -7169,7 +7185,7 @@
       </c>
       <c r="F42" s="5">
         <f t="shared" ref="F42:I42" si="5">SUM(F2:F41)</f>
-        <v>17.29</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="5"/>
@@ -7177,11 +7193,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>16.38</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -7421,7 +7437,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -7800,7 +7816,7 @@
       </c>
       <c r="B13" s="8">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>18</v>
+        <v>-11</v>
       </c>
       <c r="D13" s="7">
         <v>46284</v>
